--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_16-03-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_16-03-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="360">
   <si>
     <t>SKU</t>
   </si>
@@ -292,33 +292,36 @@
     <t>£34.43</t>
   </si>
   <si>
+    <t>Error: ("Connection broken: ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None)", ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
+  </si>
+  <si>
+    <t>£42.10</t>
+  </si>
+  <si>
+    <t>£44.80</t>
+  </si>
+  <si>
+    <t>£43.65</t>
+  </si>
+  <si>
+    <t>£925.79</t>
+  </si>
+  <si>
+    <t>£42.95</t>
+  </si>
+  <si>
+    <t>£1,195.00</t>
+  </si>
+  <si>
+    <t>£1,319.33</t>
+  </si>
+  <si>
+    <t>£1,275.65</t>
+  </si>
+  <si>
     <t>£36.99</t>
   </si>
   <si>
-    <t>£42.10</t>
-  </si>
-  <si>
-    <t>£44.80</t>
-  </si>
-  <si>
-    <t>£43.65</t>
-  </si>
-  <si>
-    <t>£925.79</t>
-  </si>
-  <si>
-    <t>£42.95</t>
-  </si>
-  <si>
-    <t>£1,195.00</t>
-  </si>
-  <si>
-    <t>£1,319.33</t>
-  </si>
-  <si>
-    <t>£1,275.65</t>
-  </si>
-  <si>
     <t>N/L</t>
   </si>
   <si>
@@ -511,9 +514,78 @@
     <t>£1276.0</t>
   </si>
   <si>
+    <t>£13.4</t>
+  </si>
+  <si>
+    <t>£15.4</t>
+  </si>
+  <si>
+    <t>£19.75</t>
+  </si>
+  <si>
+    <t>£20.1</t>
+  </si>
+  <si>
+    <t>£25.75</t>
+  </si>
+  <si>
+    <t>£27.78</t>
+  </si>
+  <si>
+    <t>£28.2</t>
+  </si>
+  <si>
+    <t>£35.2</t>
+  </si>
+  <si>
+    <t>£50.15</t>
+  </si>
+  <si>
+    <t>£42.1</t>
+  </si>
+  <si>
+    <t>£56.09</t>
+  </si>
+  <si>
+    <t>£56.75</t>
+  </si>
+  <si>
+    <t>£52.29</t>
+  </si>
+  <si>
+    <t>£1029.48</t>
+  </si>
+  <si>
+    <t>£1235.4</t>
+  </si>
+  <si>
     <t>POA</t>
   </si>
   <si>
+    <t>£59.39</t>
+  </si>
+  <si>
+    <t>£65.99</t>
+  </si>
+  <si>
+    <t>£94.27</t>
+  </si>
+  <si>
+    <t>£102.56</t>
+  </si>
+  <si>
+    <t>£98.28</t>
+  </si>
+  <si>
+    <t>£1406.4</t>
+  </si>
+  <si>
+    <t>£1688.8</t>
+  </si>
+  <si>
+    <t>£1604.48</t>
+  </si>
+  <si>
     <t>£13.29</t>
   </si>
   <si>
@@ -586,16 +658,10 @@
     <t>£60.74</t>
   </si>
   <si>
-    <t>£10.74</t>
-  </si>
-  <si>
-    <t>£13.07</t>
-  </si>
-  <si>
-    <t>£15.87</t>
-  </si>
-  <si>
-    <t>£16.96</t>
+    <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
+  </si>
+  <si>
+    <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Read timed out. (read timeout=30)</t>
   </si>
   <si>
     <t>£21.12</t>
@@ -604,9 +670,6 @@
     <t>£23.8</t>
   </si>
   <si>
-    <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
-  </si>
-  <si>
     <t>£26.23</t>
   </si>
   <si>
@@ -616,7 +679,7 @@
     <t>£35.09</t>
   </si>
   <si>
-    <t>£41.12</t>
+    <t>£36.27</t>
   </si>
   <si>
     <t>£44.39</t>
@@ -625,30 +688,18 @@
     <t>£43.55</t>
   </si>
   <si>
-    <t>£697.98</t>
-  </si>
-  <si>
-    <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Read timed out. (read timeout=30)</t>
-  </si>
-  <si>
-    <t>£48.65</t>
-  </si>
-  <si>
-    <t>£45.36</t>
-  </si>
-  <si>
-    <t>£43.3</t>
-  </si>
-  <si>
-    <t>£44.58</t>
+    <t>£939.1</t>
+  </si>
+  <si>
+    <t>£40.65</t>
+  </si>
+  <si>
+    <t>£57.54</t>
   </si>
   <si>
     <t>£1163.76</t>
   </si>
   <si>
-    <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
-  </si>
-  <si>
     <t>Price Not Found</t>
   </si>
   <si>
@@ -736,9 +787,6 @@
     <t>£1984.64</t>
   </si>
   <si>
-    <t>£23.87</t>
-  </si>
-  <si>
     <t>£27.67</t>
   </si>
   <si>
@@ -751,9 +799,6 @@
     <t>£39.12</t>
   </si>
   <si>
-    <t>£46.64</t>
-  </si>
-  <si>
     <t>£46.55</t>
   </si>
   <si>
@@ -772,7 +817,10 @@
     <t>£81.55</t>
   </si>
   <si>
-    <t>£89.87</t>
+    <t>£86.21</t>
+  </si>
+  <si>
+    <t>£51.2</t>
   </si>
   <si>
     <t>£59.2</t>
@@ -886,13 +934,7 @@
     <t>£945.0</t>
   </si>
   <si>
-    <t>£28.03</t>
-  </si>
-  <si>
-    <t>£37.07</t>
-  </si>
-  <si>
-    <t>£42.15</t>
+    <t>£34.8</t>
   </si>
   <si>
     <t>£55.13</t>
@@ -1485,43 +1527,43 @@
         <v>74</v>
       </c>
       <c r="F2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G2" t="s">
         <v>74</v>
       </c>
       <c r="H2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J2" t="s">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="K2" t="s">
-        <v>190</v>
+        <v>214</v>
       </c>
       <c r="L2" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="M2" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="N2" t="s">
-        <v>240</v>
+        <v>181</v>
       </c>
       <c r="O2" t="s">
         <v>74</v>
       </c>
       <c r="P2" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="Q2" t="s">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="R2" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1541,43 +1583,43 @@
         <v>75</v>
       </c>
       <c r="F3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G3" t="s">
         <v>75</v>
       </c>
       <c r="H3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="J3" t="s">
-        <v>167</v>
+        <v>191</v>
       </c>
       <c r="K3" t="s">
-        <v>191</v>
+        <v>214</v>
       </c>
       <c r="L3" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="M3" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="N3" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="O3" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="P3" t="s">
-        <v>281</v>
+        <v>297</v>
       </c>
       <c r="Q3" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="R3" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1597,43 +1639,43 @@
         <v>76</v>
       </c>
       <c r="F4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="J4" t="s">
-        <v>168</v>
+        <v>192</v>
       </c>
       <c r="K4" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="L4" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="M4" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="N4" t="s">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="O4" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="P4" t="s">
         <v>76</v>
       </c>
       <c r="Q4" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="R4" t="s">
-        <v>323</v>
+        <v>337</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1653,43 +1695,43 @@
         <v>77</v>
       </c>
       <c r="F5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I5" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="J5" t="s">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="K5" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="L5" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="M5" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="N5" t="s">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="O5" t="s">
         <v>77</v>
       </c>
       <c r="P5" t="s">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="Q5" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="R5" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1709,43 +1751,43 @@
         <v>78</v>
       </c>
       <c r="F6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G6" t="s">
         <v>78</v>
       </c>
       <c r="H6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I6" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="J6" t="s">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="K6" t="s">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="L6" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="M6" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="N6" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="O6" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="P6" t="s">
         <v>78</v>
       </c>
       <c r="Q6" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="R6" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1765,43 +1807,43 @@
         <v>79</v>
       </c>
       <c r="F7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I7" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="J7" t="s">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="K7" t="s">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="L7" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="M7" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="N7" t="s">
-        <v>245</v>
+        <v>181</v>
       </c>
       <c r="O7" t="s">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="P7" t="s">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="Q7" t="s">
         <v>79</v>
       </c>
       <c r="R7" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1821,43 +1863,43 @@
         <v>79</v>
       </c>
       <c r="F8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I8" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="J8" t="s">
-        <v>172</v>
+        <v>196</v>
       </c>
       <c r="K8" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="L8" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="M8" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="N8" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="O8" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="P8" t="s">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="Q8" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="R8" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1877,43 +1919,43 @@
         <v>80</v>
       </c>
       <c r="F9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G9" t="s">
         <v>80</v>
       </c>
       <c r="H9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I9" t="s">
-        <v>165</v>
+        <v>132</v>
       </c>
       <c r="J9" t="s">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="K9" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="L9" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="M9" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="N9" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="O9" t="s">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="P9" t="s">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="Q9" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="R9" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1933,43 +1975,43 @@
         <v>81</v>
       </c>
       <c r="F10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I10" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="J10" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="K10" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="L10" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="M10" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="N10" t="s">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="O10" t="s">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="P10" t="s">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="Q10" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="R10" t="s">
-        <v>329</v>
+        <v>343</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1989,43 +2031,43 @@
         <v>82</v>
       </c>
       <c r="F11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I11" t="s">
-        <v>165</v>
+        <v>84</v>
       </c>
       <c r="J11" t="s">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="K11" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="L11" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="M11" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="N11" t="s">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="O11" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="P11" t="s">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="Q11" t="s">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="R11" t="s">
-        <v>330</v>
+        <v>344</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -2045,43 +2087,43 @@
         <v>83</v>
       </c>
       <c r="F12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I12" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="J12" t="s">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="K12" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="L12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M12" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="N12" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="O12" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="P12" t="s">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="Q12" t="s">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="R12" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2101,43 +2143,43 @@
         <v>84</v>
       </c>
       <c r="F13" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I13" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="J13" t="s">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="K13" t="s">
-        <v>196</v>
+        <v>221</v>
       </c>
       <c r="L13" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="M13" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="N13" t="s">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="O13" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="P13" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="Q13" t="s">
         <v>84</v>
       </c>
       <c r="R13" t="s">
-        <v>332</v>
+        <v>346</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2157,43 +2199,43 @@
         <v>85</v>
       </c>
       <c r="F14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G14" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H14" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I14" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="J14" t="s">
-        <v>178</v>
+        <v>202</v>
       </c>
       <c r="K14" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="L14" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="M14" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="N14" t="s">
-        <v>251</v>
+        <v>266</v>
       </c>
       <c r="O14" t="s">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="P14" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="Q14" t="s">
-        <v>308</v>
+        <v>322</v>
       </c>
       <c r="R14" t="s">
-        <v>333</v>
+        <v>347</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2210,46 +2252,46 @@
         <v>86</v>
       </c>
       <c r="E15" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F15" t="s">
         <v>97</v>
       </c>
       <c r="G15" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H15" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I15" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="J15" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="K15" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="L15" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="M15" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="N15" t="s">
-        <v>165</v>
+        <v>267</v>
       </c>
       <c r="O15" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="P15" t="s">
         <v>86</v>
       </c>
       <c r="Q15" t="s">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="R15" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2269,31 +2311,31 @@
         <v>87</v>
       </c>
       <c r="F16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G16" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H16" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I16" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="J16" t="s">
-        <v>180</v>
+        <v>204</v>
       </c>
       <c r="K16" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="L16" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="M16" t="s">
-        <v>226</v>
+        <v>243</v>
       </c>
       <c r="N16" t="s">
-        <v>252</v>
+        <v>181</v>
       </c>
       <c r="O16" t="s">
         <v>87</v>
@@ -2302,10 +2344,10 @@
         <v>87</v>
       </c>
       <c r="Q16" t="s">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="R16" t="s">
-        <v>334</v>
+        <v>348</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2325,43 +2367,43 @@
         <v>88</v>
       </c>
       <c r="F17" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H17" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I17" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="J17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K17" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="L17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M17" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="N17" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="O17" t="s">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="P17" t="s">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="Q17" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="R17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2381,43 +2423,43 @@
         <v>89</v>
       </c>
       <c r="F18" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G18" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H18" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I18" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="J18" t="s">
+        <v>205</v>
+      </c>
+      <c r="K18" t="s">
+        <v>224</v>
+      </c>
+      <c r="L18" t="s">
+        <v>102</v>
+      </c>
+      <c r="M18" t="s">
+        <v>245</v>
+      </c>
+      <c r="N18" t="s">
         <v>181</v>
       </c>
-      <c r="K18" t="s">
-        <v>196</v>
-      </c>
-      <c r="L18" t="s">
-        <v>101</v>
-      </c>
-      <c r="M18" t="s">
-        <v>228</v>
-      </c>
-      <c r="N18" t="s">
-        <v>165</v>
-      </c>
       <c r="O18" t="s">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="P18" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="Q18" t="s">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="R18" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2437,43 +2479,43 @@
         <v>90</v>
       </c>
       <c r="F19" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G19" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H19" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I19" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="J19" t="s">
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="K19" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="L19" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="M19" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="N19" t="s">
-        <v>165</v>
+        <v>268</v>
       </c>
       <c r="O19" t="s">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="P19" t="s">
-        <v>290</v>
+        <v>156</v>
       </c>
       <c r="Q19" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="R19" t="s">
-        <v>336</v>
+        <v>350</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2493,43 +2535,43 @@
         <v>91</v>
       </c>
       <c r="F20" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G20" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H20" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I20" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="J20" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="K20" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="L20" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="M20" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="N20" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="O20" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="P20" t="s">
-        <v>91</v>
+        <v>306</v>
       </c>
       <c r="Q20" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="R20" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2543,49 +2585,49 @@
         <v>92</v>
       </c>
       <c r="D21" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="E21" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="F21" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H21" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I21" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="J21" t="s">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="K21" t="s">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="L21" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="M21" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="N21" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="O21" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="P21" t="s">
-        <v>291</v>
+        <v>158</v>
       </c>
       <c r="Q21" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="R21" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2605,43 +2647,43 @@
         <v>93</v>
       </c>
       <c r="F22" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G22" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H22" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I22" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="J22" t="s">
-        <v>185</v>
+        <v>209</v>
       </c>
       <c r="K22" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="L22" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="M22" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="N22" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="O22" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
       <c r="P22" t="s">
-        <v>292</v>
+        <v>159</v>
       </c>
       <c r="Q22" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="R22" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2661,43 +2703,43 @@
         <v>94</v>
       </c>
       <c r="F23" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G23" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H23" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I23" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="J23" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="K23" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="L23" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="M23" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="N23" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="O23" t="s">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="P23" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="Q23" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="R23" t="s">
-        <v>340</v>
+        <v>354</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2717,43 +2759,43 @@
         <v>95</v>
       </c>
       <c r="F24" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G24" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H24" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I24" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="J24" t="s">
-        <v>187</v>
+        <v>211</v>
       </c>
       <c r="K24" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="L24" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="M24" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="N24" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="O24" t="s">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="P24" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="Q24" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="R24" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -2773,43 +2815,43 @@
         <v>96</v>
       </c>
       <c r="F25" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G25" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H25" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I25" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J25" t="s">
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="K25" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L25" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M25" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="N25" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="O25" t="s">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="P25" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q25" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="R25" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -2829,43 +2871,43 @@
         <v>97</v>
       </c>
       <c r="F26" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G26" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H26" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I26" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="J26" t="s">
-        <v>189</v>
+        <v>213</v>
       </c>
       <c r="K26" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="L26" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="M26" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="N26" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="O26" t="s">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="P26" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="Q26" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="R26" t="s">
-        <v>342</v>
+        <v>356</v>
       </c>
     </row>
     <row r="27" spans="1:18">
@@ -2885,43 +2927,43 @@
         <v>98</v>
       </c>
       <c r="F27" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G27" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H27" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I27" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="J27" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K27" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="L27" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="M27" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="N27" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O27" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="P27" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="Q27" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="R27" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
     </row>
     <row r="28" spans="1:18">
@@ -2941,43 +2983,43 @@
         <v>99</v>
       </c>
       <c r="F28" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G28" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H28" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I28" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="J28" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K28" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="L28" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="M28" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="N28" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O28" t="s">
-        <v>278</v>
+        <v>294</v>
       </c>
       <c r="P28" t="s">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="Q28" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="R28" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
     </row>
     <row r="29" spans="1:18">
@@ -2997,43 +3039,43 @@
         <v>100</v>
       </c>
       <c r="F29" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G29" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H29" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I29" t="s">
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="J29" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K29" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="L29" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M29" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="N29" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O29" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="P29" t="s">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="Q29" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="R29" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>

--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_16-03-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_16-03-2026.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Celotex_Prices\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9F14863-91C9-4E55-85FB-BC0E50D59316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="3270" yWindow="1380" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="337">
   <si>
     <t>SKU</t>
   </si>
@@ -514,76 +520,7 @@
     <t>£1276.0</t>
   </si>
   <si>
-    <t>£13.4</t>
-  </si>
-  <si>
-    <t>£15.4</t>
-  </si>
-  <si>
-    <t>£19.75</t>
-  </si>
-  <si>
-    <t>£20.1</t>
-  </si>
-  <si>
-    <t>£25.75</t>
-  </si>
-  <si>
-    <t>£27.78</t>
-  </si>
-  <si>
-    <t>£28.2</t>
-  </si>
-  <si>
-    <t>£35.2</t>
-  </si>
-  <si>
-    <t>£50.15</t>
-  </si>
-  <si>
-    <t>£42.1</t>
-  </si>
-  <si>
-    <t>£56.09</t>
-  </si>
-  <si>
-    <t>£56.75</t>
-  </si>
-  <si>
-    <t>£52.29</t>
-  </si>
-  <si>
-    <t>£1029.48</t>
-  </si>
-  <si>
-    <t>£1235.4</t>
-  </si>
-  <si>
     <t>POA</t>
-  </si>
-  <si>
-    <t>£59.39</t>
-  </si>
-  <si>
-    <t>£65.99</t>
-  </si>
-  <si>
-    <t>£94.27</t>
-  </si>
-  <si>
-    <t>£102.56</t>
-  </si>
-  <si>
-    <t>£98.28</t>
-  </si>
-  <si>
-    <t>£1406.4</t>
-  </si>
-  <si>
-    <t>£1688.8</t>
-  </si>
-  <si>
-    <t>£1604.48</t>
   </si>
   <si>
     <t>£13.29</t>
@@ -1099,8 +1036,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1163,13 +1100,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1207,7 +1152,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1241,6 +1186,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1275,9 +1221,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1450,11 +1397,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1510,7 +1457,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -1539,34 +1486,34 @@
         <v>166</v>
       </c>
       <c r="J2" t="s">
-        <v>190</v>
+        <v>167</v>
       </c>
       <c r="K2" t="s">
-        <v>214</v>
+        <v>191</v>
       </c>
       <c r="L2" t="s">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="M2" t="s">
-        <v>229</v>
+        <v>206</v>
       </c>
       <c r="N2" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="O2" t="s">
         <v>74</v>
       </c>
       <c r="P2" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="Q2" t="s">
+        <v>290</v>
+      </c>
+      <c r="R2" t="s">
         <v>313</v>
       </c>
-      <c r="R2" t="s">
-        <v>336</v>
-      </c>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -1592,37 +1539,37 @@
         <v>142</v>
       </c>
       <c r="I3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J3" t="s">
+        <v>168</v>
+      </c>
+      <c r="K3" t="s">
         <v>191</v>
       </c>
-      <c r="K3" t="s">
-        <v>214</v>
-      </c>
       <c r="L3" t="s">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="M3" t="s">
-        <v>230</v>
+        <v>207</v>
       </c>
       <c r="N3" t="s">
-        <v>257</v>
+        <v>234</v>
       </c>
       <c r="O3" t="s">
-        <v>272</v>
+        <v>249</v>
       </c>
       <c r="P3" t="s">
-        <v>297</v>
+        <v>274</v>
       </c>
       <c r="Q3" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="R3" t="s">
-        <v>230</v>
+        <v>207</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -1648,37 +1595,37 @@
         <v>143</v>
       </c>
       <c r="I4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="J4" t="s">
-        <v>192</v>
+        <v>169</v>
       </c>
       <c r="K4" t="s">
-        <v>214</v>
+        <v>191</v>
       </c>
       <c r="L4" t="s">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="M4" t="s">
-        <v>231</v>
+        <v>208</v>
       </c>
       <c r="N4" t="s">
-        <v>258</v>
+        <v>235</v>
       </c>
       <c r="O4" t="s">
-        <v>273</v>
+        <v>250</v>
       </c>
       <c r="P4" t="s">
         <v>76</v>
       </c>
       <c r="Q4" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="R4" t="s">
-        <v>337</v>
+        <v>314</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -1704,37 +1651,37 @@
         <v>144</v>
       </c>
       <c r="I5" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="J5" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="K5" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
       <c r="L5" t="s">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="M5" t="s">
-        <v>232</v>
+        <v>209</v>
       </c>
       <c r="N5" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="O5" t="s">
         <v>77</v>
       </c>
       <c r="P5" t="s">
-        <v>298</v>
+        <v>275</v>
       </c>
       <c r="Q5" t="s">
-        <v>316</v>
+        <v>293</v>
       </c>
       <c r="R5" t="s">
-        <v>338</v>
+        <v>315</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -1760,37 +1707,37 @@
         <v>145</v>
       </c>
       <c r="I6" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="J6" t="s">
-        <v>194</v>
+        <v>171</v>
       </c>
       <c r="K6" t="s">
-        <v>216</v>
+        <v>193</v>
       </c>
       <c r="L6" t="s">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="M6" t="s">
-        <v>233</v>
+        <v>210</v>
       </c>
       <c r="N6" t="s">
-        <v>260</v>
+        <v>237</v>
       </c>
       <c r="O6" t="s">
-        <v>274</v>
+        <v>251</v>
       </c>
       <c r="P6" t="s">
         <v>78</v>
       </c>
       <c r="Q6" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="R6" t="s">
-        <v>339</v>
+        <v>316</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -1816,37 +1763,37 @@
         <v>146</v>
       </c>
       <c r="I7" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="J7" t="s">
-        <v>195</v>
+        <v>172</v>
       </c>
       <c r="K7" t="s">
-        <v>217</v>
+        <v>194</v>
       </c>
       <c r="L7" t="s">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="M7" t="s">
-        <v>234</v>
+        <v>211</v>
       </c>
       <c r="N7" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="O7" t="s">
-        <v>275</v>
+        <v>252</v>
       </c>
       <c r="P7" t="s">
-        <v>299</v>
+        <v>276</v>
       </c>
       <c r="Q7" t="s">
         <v>79</v>
       </c>
       <c r="R7" t="s">
-        <v>340</v>
+        <v>317</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -1872,37 +1819,37 @@
         <v>146</v>
       </c>
       <c r="I8" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="J8" t="s">
-        <v>196</v>
+        <v>173</v>
       </c>
       <c r="K8" t="s">
-        <v>214</v>
+        <v>191</v>
       </c>
       <c r="L8" t="s">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="M8" t="s">
-        <v>235</v>
+        <v>212</v>
       </c>
       <c r="N8" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="O8" t="s">
+        <v>253</v>
+      </c>
+      <c r="P8" t="s">
         <v>276</v>
       </c>
-      <c r="P8" t="s">
-        <v>299</v>
-      </c>
       <c r="Q8" t="s">
+        <v>295</v>
+      </c>
+      <c r="R8" t="s">
         <v>318</v>
       </c>
-      <c r="R8" t="s">
-        <v>341</v>
-      </c>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1928,37 +1875,37 @@
         <v>147</v>
       </c>
       <c r="I9" t="s">
-        <v>132</v>
+        <v>166</v>
       </c>
       <c r="J9" t="s">
-        <v>197</v>
+        <v>174</v>
       </c>
       <c r="K9" t="s">
-        <v>218</v>
+        <v>195</v>
       </c>
       <c r="L9" t="s">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="M9" t="s">
-        <v>236</v>
+        <v>213</v>
       </c>
       <c r="N9" t="s">
-        <v>262</v>
+        <v>239</v>
       </c>
       <c r="O9" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="P9" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="Q9" t="s">
+        <v>296</v>
+      </c>
+      <c r="R9" t="s">
         <v>319</v>
       </c>
-      <c r="R9" t="s">
-        <v>342</v>
-      </c>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -1984,37 +1931,37 @@
         <v>148</v>
       </c>
       <c r="I10" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="J10" t="s">
-        <v>198</v>
+        <v>175</v>
       </c>
       <c r="K10" t="s">
-        <v>219</v>
+        <v>196</v>
       </c>
       <c r="L10" t="s">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="M10" t="s">
-        <v>237</v>
+        <v>214</v>
       </c>
       <c r="N10" t="s">
-        <v>263</v>
+        <v>240</v>
       </c>
       <c r="O10" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="P10" t="s">
-        <v>300</v>
+        <v>277</v>
       </c>
       <c r="Q10" t="s">
+        <v>297</v>
+      </c>
+      <c r="R10" t="s">
         <v>320</v>
       </c>
-      <c r="R10" t="s">
-        <v>343</v>
-      </c>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -2040,37 +1987,37 @@
         <v>149</v>
       </c>
       <c r="I11" t="s">
-        <v>84</v>
+        <v>166</v>
       </c>
       <c r="J11" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="K11" t="s">
-        <v>219</v>
+        <v>196</v>
       </c>
       <c r="L11" t="s">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="M11" t="s">
-        <v>238</v>
+        <v>215</v>
       </c>
       <c r="N11" t="s">
-        <v>264</v>
+        <v>241</v>
       </c>
       <c r="O11" t="s">
-        <v>279</v>
+        <v>256</v>
       </c>
       <c r="P11" t="s">
-        <v>301</v>
+        <v>278</v>
       </c>
       <c r="Q11" t="s">
+        <v>298</v>
+      </c>
+      <c r="R11" t="s">
         <v>321</v>
       </c>
-      <c r="R11" t="s">
-        <v>344</v>
-      </c>
     </row>
-    <row r="12" spans="1:18">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -2096,37 +2043,37 @@
         <v>102</v>
       </c>
       <c r="I12" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="J12" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="K12" t="s">
-        <v>220</v>
+        <v>197</v>
       </c>
       <c r="L12" t="s">
         <v>102</v>
       </c>
       <c r="M12" t="s">
-        <v>239</v>
+        <v>216</v>
       </c>
       <c r="N12" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="O12" t="s">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="P12" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="Q12" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="R12" t="s">
-        <v>345</v>
+        <v>322</v>
       </c>
     </row>
-    <row r="13" spans="1:18">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -2152,37 +2099,37 @@
         <v>150</v>
       </c>
       <c r="I13" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="J13" t="s">
-        <v>201</v>
+        <v>178</v>
       </c>
       <c r="K13" t="s">
-        <v>221</v>
+        <v>198</v>
       </c>
       <c r="L13" t="s">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="M13" t="s">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="N13" t="s">
-        <v>265</v>
+        <v>242</v>
       </c>
       <c r="O13" t="s">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="P13" t="s">
-        <v>302</v>
+        <v>279</v>
       </c>
       <c r="Q13" t="s">
         <v>84</v>
       </c>
       <c r="R13" t="s">
-        <v>346</v>
+        <v>323</v>
       </c>
     </row>
-    <row r="14" spans="1:18">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>30</v>
       </c>
@@ -2208,37 +2155,37 @@
         <v>151</v>
       </c>
       <c r="I14" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="J14" t="s">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="K14" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
       <c r="L14" t="s">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="M14" t="s">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="N14" t="s">
-        <v>266</v>
+        <v>243</v>
       </c>
       <c r="O14" t="s">
-        <v>282</v>
+        <v>259</v>
       </c>
       <c r="P14" t="s">
-        <v>303</v>
+        <v>280</v>
       </c>
       <c r="Q14" t="s">
-        <v>322</v>
+        <v>299</v>
       </c>
       <c r="R14" t="s">
-        <v>347</v>
+        <v>324</v>
       </c>
     </row>
-    <row r="15" spans="1:18">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -2264,37 +2211,37 @@
         <v>152</v>
       </c>
       <c r="I15" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="J15" t="s">
-        <v>203</v>
+        <v>180</v>
       </c>
       <c r="K15" t="s">
-        <v>222</v>
+        <v>199</v>
       </c>
       <c r="L15" t="s">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="M15" t="s">
-        <v>242</v>
+        <v>219</v>
       </c>
       <c r="N15" t="s">
-        <v>267</v>
+        <v>244</v>
       </c>
       <c r="O15" t="s">
-        <v>283</v>
+        <v>260</v>
       </c>
       <c r="P15" t="s">
         <v>86</v>
       </c>
       <c r="Q15" t="s">
-        <v>323</v>
+        <v>300</v>
       </c>
       <c r="R15" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="16" spans="1:18">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -2320,22 +2267,22 @@
         <v>153</v>
       </c>
       <c r="I16" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="J16" t="s">
-        <v>204</v>
+        <v>181</v>
       </c>
       <c r="K16" t="s">
-        <v>223</v>
+        <v>200</v>
       </c>
       <c r="L16" t="s">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="M16" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="N16" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="O16" t="s">
         <v>87</v>
@@ -2344,13 +2291,13 @@
         <v>87</v>
       </c>
       <c r="Q16" t="s">
-        <v>324</v>
+        <v>301</v>
       </c>
       <c r="R16" t="s">
-        <v>348</v>
+        <v>325</v>
       </c>
     </row>
-    <row r="17" spans="1:18">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -2376,37 +2323,37 @@
         <v>154</v>
       </c>
       <c r="I17" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="J17" t="s">
         <v>102</v>
       </c>
       <c r="K17" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
       <c r="L17" t="s">
         <v>102</v>
       </c>
       <c r="M17" t="s">
-        <v>244</v>
+        <v>221</v>
       </c>
       <c r="N17" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="O17" t="s">
-        <v>284</v>
+        <v>261</v>
       </c>
       <c r="P17" t="s">
-        <v>304</v>
+        <v>281</v>
       </c>
       <c r="Q17" t="s">
-        <v>325</v>
+        <v>302</v>
       </c>
       <c r="R17" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="18" spans="1:18">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -2432,37 +2379,37 @@
         <v>155</v>
       </c>
       <c r="I18" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="J18" t="s">
-        <v>205</v>
+        <v>182</v>
       </c>
       <c r="K18" t="s">
-        <v>224</v>
+        <v>201</v>
       </c>
       <c r="L18" t="s">
         <v>102</v>
       </c>
       <c r="M18" t="s">
-        <v>245</v>
+        <v>222</v>
       </c>
       <c r="N18" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="O18" t="s">
-        <v>285</v>
+        <v>262</v>
       </c>
       <c r="P18" t="s">
-        <v>305</v>
+        <v>282</v>
       </c>
       <c r="Q18" t="s">
+        <v>303</v>
+      </c>
+      <c r="R18" t="s">
         <v>326</v>
       </c>
-      <c r="R18" t="s">
-        <v>349</v>
-      </c>
     </row>
-    <row r="19" spans="1:18">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>35</v>
       </c>
@@ -2488,37 +2435,37 @@
         <v>156</v>
       </c>
       <c r="I19" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="J19" t="s">
-        <v>206</v>
+        <v>183</v>
       </c>
       <c r="K19" t="s">
-        <v>225</v>
+        <v>202</v>
       </c>
       <c r="L19" t="s">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="M19" t="s">
-        <v>246</v>
+        <v>223</v>
       </c>
       <c r="N19" t="s">
-        <v>268</v>
+        <v>245</v>
       </c>
       <c r="O19" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="P19" t="s">
         <v>156</v>
       </c>
       <c r="Q19" t="s">
+        <v>304</v>
+      </c>
+      <c r="R19" t="s">
         <v>327</v>
       </c>
-      <c r="R19" t="s">
-        <v>350</v>
-      </c>
     </row>
-    <row r="20" spans="1:18">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -2544,37 +2491,37 @@
         <v>157</v>
       </c>
       <c r="I20" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="J20" t="s">
-        <v>207</v>
+        <v>184</v>
       </c>
       <c r="K20" t="s">
-        <v>214</v>
+        <v>191</v>
       </c>
       <c r="L20" t="s">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="M20" t="s">
-        <v>247</v>
+        <v>224</v>
       </c>
       <c r="N20" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="O20" t="s">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="P20" t="s">
-        <v>306</v>
+        <v>283</v>
       </c>
       <c r="Q20" t="s">
+        <v>305</v>
+      </c>
+      <c r="R20" t="s">
         <v>328</v>
       </c>
-      <c r="R20" t="s">
-        <v>351</v>
-      </c>
     </row>
-    <row r="21" spans="1:18">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>37</v>
       </c>
@@ -2600,22 +2547,22 @@
         <v>158</v>
       </c>
       <c r="I21" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="J21" t="s">
-        <v>208</v>
+        <v>185</v>
       </c>
       <c r="K21" t="s">
-        <v>226</v>
+        <v>203</v>
       </c>
       <c r="L21" t="s">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="M21" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="N21" t="s">
-        <v>270</v>
+        <v>247</v>
       </c>
       <c r="O21" t="s">
         <v>101</v>
@@ -2624,13 +2571,13 @@
         <v>158</v>
       </c>
       <c r="Q21" t="s">
+        <v>306</v>
+      </c>
+      <c r="R21" t="s">
         <v>329</v>
       </c>
-      <c r="R21" t="s">
-        <v>352</v>
-      </c>
     </row>
-    <row r="22" spans="1:18">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>38</v>
       </c>
@@ -2656,37 +2603,37 @@
         <v>159</v>
       </c>
       <c r="I22" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="J22" t="s">
-        <v>209</v>
+        <v>186</v>
       </c>
       <c r="K22" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
       <c r="L22" t="s">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="M22" t="s">
-        <v>249</v>
+        <v>226</v>
       </c>
       <c r="N22" t="s">
-        <v>271</v>
+        <v>248</v>
       </c>
       <c r="O22" t="s">
-        <v>288</v>
+        <v>265</v>
       </c>
       <c r="P22" t="s">
         <v>159</v>
       </c>
       <c r="Q22" t="s">
+        <v>307</v>
+      </c>
+      <c r="R22" t="s">
         <v>330</v>
       </c>
-      <c r="R22" t="s">
-        <v>353</v>
-      </c>
     </row>
-    <row r="23" spans="1:18">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>39</v>
       </c>
@@ -2712,37 +2659,37 @@
         <v>160</v>
       </c>
       <c r="I23" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="J23" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="K23" t="s">
-        <v>214</v>
+        <v>191</v>
       </c>
       <c r="L23" t="s">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="M23" t="s">
-        <v>250</v>
+        <v>227</v>
       </c>
       <c r="N23" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="O23" t="s">
-        <v>289</v>
+        <v>266</v>
       </c>
       <c r="P23" t="s">
-        <v>307</v>
+        <v>284</v>
       </c>
       <c r="Q23" t="s">
+        <v>308</v>
+      </c>
+      <c r="R23" t="s">
         <v>331</v>
       </c>
-      <c r="R23" t="s">
-        <v>354</v>
-      </c>
     </row>
-    <row r="24" spans="1:18">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>40</v>
       </c>
@@ -2768,37 +2715,37 @@
         <v>161</v>
       </c>
       <c r="I24" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="J24" t="s">
-        <v>211</v>
+        <v>188</v>
       </c>
       <c r="K24" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
       <c r="L24" t="s">
+        <v>205</v>
+      </c>
+      <c r="M24" t="s">
         <v>228</v>
       </c>
-      <c r="M24" t="s">
-        <v>251</v>
-      </c>
       <c r="N24" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="O24" t="s">
-        <v>290</v>
+        <v>267</v>
       </c>
       <c r="P24" t="s">
-        <v>308</v>
+        <v>285</v>
       </c>
       <c r="Q24" t="s">
+        <v>309</v>
+      </c>
+      <c r="R24" t="s">
         <v>332</v>
       </c>
-      <c r="R24" t="s">
-        <v>355</v>
-      </c>
     </row>
-    <row r="25" spans="1:18">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>41</v>
       </c>
@@ -2827,7 +2774,7 @@
         <v>102</v>
       </c>
       <c r="J25" t="s">
-        <v>212</v>
+        <v>189</v>
       </c>
       <c r="K25" t="s">
         <v>102</v>
@@ -2836,13 +2783,13 @@
         <v>102</v>
       </c>
       <c r="M25" t="s">
-        <v>252</v>
+        <v>229</v>
       </c>
       <c r="N25" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="O25" t="s">
-        <v>291</v>
+        <v>268</v>
       </c>
       <c r="P25" t="s">
         <v>102</v>
@@ -2854,7 +2801,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="26" spans="1:18">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>42</v>
       </c>
@@ -2880,37 +2827,37 @@
         <v>162</v>
       </c>
       <c r="I26" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="J26" t="s">
-        <v>213</v>
+        <v>190</v>
       </c>
       <c r="K26" t="s">
-        <v>214</v>
+        <v>191</v>
       </c>
       <c r="L26" t="s">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="M26" t="s">
-        <v>253</v>
+        <v>230</v>
       </c>
       <c r="N26" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="O26" t="s">
-        <v>292</v>
+        <v>269</v>
       </c>
       <c r="P26" t="s">
-        <v>309</v>
+        <v>286</v>
       </c>
       <c r="Q26" t="s">
+        <v>310</v>
+      </c>
+      <c r="R26" t="s">
         <v>333</v>
       </c>
-      <c r="R26" t="s">
-        <v>356</v>
-      </c>
     </row>
-    <row r="27" spans="1:18">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>43</v>
       </c>
@@ -2936,37 +2883,37 @@
         <v>163</v>
       </c>
       <c r="I27" t="s">
-        <v>187</v>
+        <v>166</v>
       </c>
       <c r="J27" t="s">
         <v>102</v>
       </c>
       <c r="K27" t="s">
-        <v>227</v>
+        <v>204</v>
       </c>
       <c r="L27" t="s">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="M27" t="s">
-        <v>254</v>
+        <v>231</v>
       </c>
       <c r="N27" t="s">
         <v>102</v>
       </c>
       <c r="O27" t="s">
-        <v>293</v>
+        <v>270</v>
       </c>
       <c r="P27" t="s">
-        <v>310</v>
+        <v>287</v>
       </c>
       <c r="Q27" t="s">
+        <v>311</v>
+      </c>
+      <c r="R27" t="s">
         <v>334</v>
       </c>
-      <c r="R27" t="s">
-        <v>357</v>
-      </c>
     </row>
-    <row r="28" spans="1:18">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>44</v>
       </c>
@@ -2992,37 +2939,37 @@
         <v>164</v>
       </c>
       <c r="I28" t="s">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="J28" t="s">
         <v>102</v>
       </c>
       <c r="K28" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
       <c r="L28" t="s">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="M28" t="s">
-        <v>255</v>
+        <v>232</v>
       </c>
       <c r="N28" t="s">
         <v>102</v>
       </c>
       <c r="O28" t="s">
-        <v>294</v>
+        <v>271</v>
       </c>
       <c r="P28" t="s">
-        <v>311</v>
+        <v>288</v>
       </c>
       <c r="Q28" t="s">
+        <v>312</v>
+      </c>
+      <c r="R28" t="s">
         <v>335</v>
       </c>
-      <c r="R28" t="s">
-        <v>358</v>
-      </c>
     </row>
-    <row r="29" spans="1:18">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>45</v>
       </c>
@@ -3048,34 +2995,34 @@
         <v>165</v>
       </c>
       <c r="I29" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="J29" t="s">
         <v>102</v>
       </c>
       <c r="K29" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
       <c r="L29" t="s">
         <v>102</v>
       </c>
       <c r="M29" t="s">
-        <v>256</v>
+        <v>233</v>
       </c>
       <c r="N29" t="s">
         <v>102</v>
       </c>
       <c r="O29" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="P29" t="s">
-        <v>312</v>
+        <v>289</v>
       </c>
       <c r="Q29" t="s">
         <v>102</v>
       </c>
       <c r="R29" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
     </row>
   </sheetData>
